--- a/errori-fr.xlsx
+++ b/errori-fr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f.refrigeri\Documents\Documenti Flavio\MicroserviziWeb\micro-tools-suite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A605DB-1395-4A52-8ABB-2AB825C2AD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82CAB4A-9BF4-4A6F-B1B5-3FEB61CF6041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="95">
   <si>
     <t>Marque</t>
   </si>
@@ -1165,12 +1165,135 @@
 Éteignez et débranchez la friteuse et laissez-la refroidir complètement.
 Si l'écran continue d'afficher "E28", contactez le Service Après-Vente (voir page 25).</t>
   </si>
+  <si>
+    <t>Xiaomi</t>
+  </si>
+  <si>
+    <t>Xiaomi Dual Zone Air Fryer 10L</t>
+  </si>
+  <si>
+    <t>MAF-D1001</t>
+  </si>
+  <si>
+    <t>Nome
+Xiaomi Dual Zone Air Fryer 10L
+Modello
+MAF-D1001
+Colore
+Nero
+Potenza nominale
+2.700 W (1.150 W a sinistra + 1.450 W a destra)
+Tensione nominale
+220-240 V~
+Frequenza nominale
+50-60 Hz
+Capacità nominale
+10 L (3,5 L a sinistra + 6,5 L a destra)</t>
+  </si>
+  <si>
+    <t>Xiaomi MAF-D1001 Smart Double Stack Air Fryer User Manual - Manuals+</t>
+  </si>
+  <si>
+    <t>Xiaomi Air Fryer 6,5L</t>
+  </si>
+  <si>
+    <t>MAF-W6051</t>
+  </si>
+  <si>
+    <t>Troubleshooting - Xiaomi Smart Air Fryer 6,5 User Manual [Page 10] | ManualsLib</t>
+  </si>
+  <si>
+    <t>Nom du produit Xiaomi Air Fryer 6,5L Modèle du produit MAF-W6051 Couleur du produit Blanc Noir Puissance nominale 1700 W Tension nominale 220-240 V~ Fréquence nominale 50-60 Hz Capacité nominale 6,5 L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"La friteuse à air ne fonctionne pas."
+Classification : Vérification de l'Alimentation / Assemblage
+Gravité : Basse  
+"E1"
+Classification : Réparation Matérielle
+Gravité : Haute   
+"E2"
+Classification : Réparation Matérielle
+Gravité : Haute   
+"Le ventilateur ne tourne pas."
+Classification : Réparation Matérielle
+Gravité : Haute   
+"De la fumée blanche sort."
+Classification : Nettoyage / Fonctionnement Normal
+Gravité : Basse   
+"Impossible d'insérer le panier dans la friteuse à air en douceur."
+Classification : Erreur d'Utilisation / Capacité
+Gravité : Basse </t>
+  </si>
+  <si>
+    <t>"La friteuse à air ne fonctionne pas."
+Classification : Vérification de l'Alimentation / Assemblage
+Gravité : Basse
+"E1"
+Classification : Réparation Matérielle
+Gravité : Haute
+"E2"
+Classification : Réparation Matérielle
+Gravité : Haute
+"Le ventilateur ne tourne pas."
+Classification : Réparation Matérielle
+Gravité : Haute
+"De la fumée blanche sort."
+Classification : Nettoyage / Fonctionnement Normal
+Gravité : Basse
+"Impossible d'insérer le panier dans la friteuse à air en douceur."
+Classification : Erreur d'Utilisation / Capacité
+Gravité : Basse
+"La fonction de programmation ne fonctionne pas comme demandé."
+Classification : Erreur Logicielle / Configuration
+Gravité : Basse
+"Impossible de se connecter au Wi-Fi."
+Classification : Erreur de Réseau / Application
+Gravité : Basse
+"Impossible de connecter la friteuse à air."
+Classification : Erreur de Réseau / Application
+Gravité : Basse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"La friteuse à air ne fonctionne pas."
+La friteuse à air n'est pas connectée à une alimentation électrique ; branchez le cordon d'alimentation sur une prise électrique mise à la terre. Le panier n'est pas poussé en place ; retirez le panier et repoussez-le en place.  
+ "E1"
+Le capteur présente un circuit ouvert ; contactez l'équipe du service après-vente.   
+"E2"
+Le capteur présente un court-circuit ; contactez l'équipe du service après-vente.   
+"Le ventilateur ne tourne pas."
+La pale du ventilateur est coincée ; contactez l'équipe du service après-vente. Le moteur est endommagé ou d'autres composants présentent un circuit rompu ; contactez l'équipe du service après-vente.   
+"De la fumée blanche sort."
+Cuisson d'ingrédients gras : lorsque vous faites frire des ingrédients contenant plus de graisse, il y aura beaucoup de fumée, ce qui est normal. La friteuse à air contient encore des résidus de graisse du programme de cuisson précédent ; assurez-vous de nettoyer la friteuse à air après chaque programme de cuisson.   
+"Impossible d'insérer le panier dans la friteuse à air en douceur."
+Trop d'ingrédients dans le panier ; les ingrédients dans le panier ne peuvent pas dépasser la marque maximale. Le panier n'est pas correctement inséré ; insérez correctement le panier.  </t>
+  </si>
+  <si>
+    <t>"La friteuse à air ne fonctionne pas."
+La friteuse à air n'est pas connectée à une alimentation électrique ; branchez le cordon d'alimentation sur une prise électrique mise à la terre. Le panier n'est pas poussé en place ; retirez le panier et repoussez-le en place.
+"E1"
+Le capteur présente un circuit ouvert ; contactez l'équipe du service après-vente.
+"E2"
+Le capteur présente un court-circuit ; contactez l'équipe du service après-vente.
+"Le ventilateur ne tourne pas."
+La pale du ventilateur est coincée ; contactez l'équipe du service après-vente. Le moteur est endommagé ou d'autres composants présentent un circuit rompu ; contactez l'équipe du service après-vente.
+"De la fumée blanche sort."
+Cuisson d'ingrédients gras : lorsque vous faites frire des ingrédients contenant plus de graisse, il y aura beaucoup de fumée, ce qui est normal. La friteuse à air contient encore des résidus de graisse du programme de cuisson précédent ; assurez-vous de nettoyer la friteuse à air après chaque programme de cuisson.
+"Impossible d'insérer le panier dans la friteuse à air en douceur."
+Trop d'ingrédients dans le panier ; les ingrédients dans le panier ne peuvent pas dépasser la marque maximale. Le panier n'est pas correctement inséré ; insérez correctement le panier.
+"La fonction de programmation ne fonctionne pas comme demandé."
+Le temps programmé est trop court ; le temps programmé doit être plus long que le temps de cuisson. Le temps programmé n'est pas enregistré ; le temps programmé doit être enregistré et exécuté en appuyant sur le bouton de commande.
+"Impossible de se connecter au Wi-Fi."
+L'application Mi Home/Xiaomi Home n'est pas à la dernière version ; mettez à jour l'application Mi Home/Xiaomi Home vers la dernière version. Le signal Wi-Fi est faible ; déplacez-vous vers un endroit où le signal est suffisamment fort.
+"Impossible de connecter la friteuse à air."
+Impossible de se connecter au Wi-Fi ; vérifiez si le Wi-Fi est connecté normalement ou réinitialisez le Wi-Fi pour vous reconnecter.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1194,6 +1317,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF5D5D5D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1216,7 +1345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1239,6 +1368,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -1574,7 +1709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
@@ -1973,6 +2108,53 @@
         <v>72</v>
       </c>
     </row>
+    <row r="15" spans="1:9" ht="345" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1981,8 +2163,10 @@
     <hyperlink ref="H5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="B13" r:id="rId5" display="https://cosori.com/collections/air-fryers/products/cosori-9-0-quart-dual-basket-air-fryer" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="B14" r:id="rId6" display="https://cosori.com/collections/air-fryers/products/pro-le-5-0-quart-air-fryer" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="G15" r:id="rId7" display="https://it.manuals.plus/xiaomi/maf-d1001-smart-double-stack-air-fryer-manual" xr:uid="{0AB611C0-46D8-4F45-ACF1-8440E73A64BF}"/>
+    <hyperlink ref="G16" r:id="rId8" display="https://www.manualslib.com/manual/3272450/Xiaomi-Smart-Air-Fryer-6-5.html?page=10" xr:uid="{00EDAB9B-306B-4972-A514-01C3995D2114}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>